--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -35,12 +35,22 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,13 +75,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -535,7 +551,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -558,8 +574,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>packages/accounting/src/statutory.ts, statutory-report.ts; tests/unit/architecture.test.ts ('no transaction module reads the reporting framework', 'statutory statements read the ledger and the reporting framework only', 'one writer per side'); tests/api/statutory.test.ts</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Statements and validations come only from the framework tables; disclosure rules are stored as data and rendered in V2-M5 from the same tables. The expression interpreter has no code evaluation (architecture-tested).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -584,7 +608,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -607,8 +631,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>migration 20260119000000_v2_reporting_framework; tests/api/statutory.test.ts ('a second standard with another layout ... when the year switches to it')</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Standard, effective-dated version, statement lines, map, disclosure rules and validation rules are tables keyed to the version; company_reporting_framework selects one per financial year; switching the year's version changed the output with no code change.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -633,7 +665,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -656,8 +688,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m1-micro-synthetic.json (version and alternative); tests/api/statutory.test.ts</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Two synthetic standards with different layouts produce their own hand-calculated statements from one ledger. A third standard is a further set of API calls (no code path names a standard). No real FRS 102 or FRS 105 content is entered (DEC-052).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -680,9 +720,9 @@
           <t>V2-M1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -705,8 +745,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/statutory.test.ts ('verification by a second person'); tests/db/reporting-framework.test.ts ('verification: once, by a person other than the author ...')</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Built and tested: author cannot verify (service 403 and database CHECK), verified version and its content immutable (service 409 and database trigger), changes supersede, unverified previews carry verified=false and a PREVIEW ONLY notice. Remaining: the filing-ready refusal of unverified rules lands with V2-M6. No real rule is verified until the firm names its qualified accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -731,7 +779,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,10 +802,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>migration 20260119000000_v2_reporting_framework; tests/api/statutory.test.ts ('a change supersedes ... the earlier year keeps the version it was prepared under, and its figures')</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Carried from the V1 matrix (VAT rates already effective-dated there)</t>
+          <t>Mechanism only: reporting maps are in the database per effective-dated, sourced version with verification status; after a later version replaced it, the 2025 preview still came from the version 2025 chose, with the same figures. V1 management statements keep the code registry (ADR-48). The rules the firm enters remain its own and unverified until its accountant verifies them (DEC-052).</t>
         </is>
       </c>
     </row>
@@ -782,7 +834,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -833,7 +885,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -856,8 +908,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/statutory.test.ts (golden: unplacedAccounts empty; broken map lists the bank loan); tests/db/reporting-framework.test.ts (unique map entry and active override)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>An override wins, else the most specific map entry, else the generic one (DEC-055). Double mapping cannot occur: the database allows one live entry per (version, V1 line, subtype) and one active override per account; the preview lists unmapped and misplaced accounts and proves the P&amp;L against the ledger and the balance sheet to zero.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -880,7 +940,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -929,7 +989,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -978,7 +1038,7 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1027,7 +1087,7 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1076,7 +1136,7 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1125,7 +1185,7 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1174,7 +1234,7 @@
           <t>V2-M4</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1223,7 +1283,7 @@
           <t>V2-M4</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1274,7 +1334,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1297,8 +1357,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/statutory.test.ts (golden comparative 2025 on the 2026 version)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>The prior framework year (else the twelve months before) on the current year's version, from journal lines.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1321,7 +1389,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1370,7 +1438,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1419,7 +1487,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1468,7 +1536,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1517,7 +1585,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1566,7 +1634,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1615,7 +1683,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1664,7 +1732,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1713,7 +1781,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1762,7 +1830,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1811,7 +1879,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1860,7 +1928,7 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1909,7 +1977,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1958,7 +2026,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2007,7 +2075,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2056,7 +2124,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2105,7 +2173,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2154,7 +2222,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2203,7 +2271,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2252,7 +2320,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2301,7 +2369,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2350,7 +2418,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2399,7 +2467,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2448,7 +2516,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2497,7 +2565,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2546,7 +2614,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2595,7 +2663,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2644,7 +2712,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2693,7 +2761,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2742,7 +2810,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2791,7 +2859,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2842,7 +2910,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2865,8 +2933,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts ('reproduces the hand-written P&amp;L and balance sheet to the cent, with the comparative')</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Matched to the cent through a verified synthetic version (synthetic layout, not a real standard).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2889,7 +2965,7 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2938,7 +3014,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2987,7 +3063,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3036,7 +3112,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3085,7 +3161,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3134,7 +3210,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3183,7 +3259,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3232,7 +3308,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3281,7 +3357,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3330,7 +3406,7 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3379,9 +3455,9 @@
           <t>V2-M1</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3404,8 +3480,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3428,7 +3512,7 @@
           <t>V2-M7</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3585,7 +3669,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>specified (v2-plan.md section 3)</t>
+          <t>BUILT 2026-10-18 (acceptance package v2-m1-acceptance.md); rules unverified until the named accountant</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3600,7 +3684,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 3.5</t>
+          <t>v2-plan.md section 3.5; v2-m1-acceptance.md</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3612,7 +3696,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3910,7 +3994,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -3920,7 +4004,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3930,7 +4014,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -3960,7 +4044,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3987,7 +4071,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4022,6 +4106,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v1.1 (2026-10-18, V2-M1, DEC-055): reporting framework built. Missing -&gt; Implemented: V2-ARC-01, V2-ARC-02, V2-ARC-03, MAN-ACC-09, V2-MOD-02, V2-MOD-11, V2-OUT-06. Missing -&gt; Partially: V2-ARC-04 (filing-ready refusal in V2-M6), V2-TEST-01 (further scenarios; review by the named accountant). No real standard content entered or verified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RECORDED 2026-10-17 (DEC-051..054, ADR-62..64)</t>
+          <t>RECORDED 2026-10-17 (DEC-051..054, ADR-62..64); qualified accountant named 2026-10-18: Shoaib (DEC-056)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-18 (acceptance package v2-m1-acceptance.md); rules unverified until the named accountant</t>
+          <t>ACCEPTED under the delegation 2026-10-18 (v2-m1-acceptance.md; CI 39083312122 on fd0f556); rules unverified until Shoaib verifies them (DEC-056)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4053,7 +4053,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fd0f556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4061,7 +4065,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39083312122</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4086,7 +4094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4113,6 +4121,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v1.2 (2026-10-18, DEC-056): V2-M1 evidence recorded (CI 39083312122 and CodeQL green on fd0f556; clean clone 1977 tests, e2e 21/21). Qualified accountant named: Shoaib; no row changes status from the naming alone.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -940,9 +940,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -965,8 +965,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>packages/accounting/src/fixed-assets.ts; tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>The register: classes, additions, depreciation, disposals, changes of estimate and the ledger reconciliation (V2-FA-01..08).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -989,9 +997,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1014,8 +1022,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>packages/accounting/src/depreciation-math.ts, fixed-assets.ts (DepreciationService); tests/api/fixed-assets.test.ts ('the golden scenario'); tests/platform/fixed-assets.test.ts ('FIXED_ASSET_DEPRECIATION and its reversal'); tests/rules/posting-rules.ts</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Runs post through the PostingService (FIXED_ASSET_DEPRECIATION): one journal, a pair of lines per class, one line per asset. A run must be later than every live run, one live run per date. Only the latest live run is reversed, by its own mirror. The source has its five test categories in the registry.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1585,9 +1601,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1610,8 +1626,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Three kinds: POSTED (Dr cost / Cr a non-control offset), LINKED to the posting that already carries the cost (over-linking refused), TAKE_ON with accumulated depreciation. Reversal of a POSTED addition before any depreciation (VOID).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1634,9 +1658,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1659,8 +1683,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Full disposals: catch-up to the disposal date, cost and accumulated depreciation removed, carrying amount and proceeds on the class disposal account; gain or loss = proceeds - carrying amount. Reversed by its mirror while no later run is live. Partial disposals are out of scope (DEC-058).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1683,9 +1715,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1708,8 +1740,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>packages/accounting/src/depreciation-math.ts; tests/unit/depreciation-math.test.ts; tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Straight line and reducing balance, DAILY or MONTHLY convention; exact decimals; each charge = cumulative due (rounded half-up) - charged, so rounding never drifts.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1732,9 +1772,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1757,8 +1797,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Life in months per class default or per asset; for a take-on, the remaining life; changed prospectively by a change of estimate (append-only bases).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1781,9 +1829,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1806,8 +1854,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Residual per asset (class default as a percentage of cost); straight line depreciates to it exactly; reducing balance never goes below it.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1830,9 +1886,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1855,8 +1911,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>migration 20260120000000_v2_fixed_assets; tests/db/fixed-assets.test.ts ('classes'); tests/api/fixed-assets.test.ts ('classes name four accounts ...')</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>A class holds the four non-control accounts of the right type and subtype (database trigger) and the defaults for new assets; its code and accounts never move.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1879,9 +1943,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1904,8 +1968,16 @@
           <t>Capital allowances computations (V4)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>tests/unit/architecture.test.ts ('depreciation never reads the tax fields'); tests/api/fixed-assets.test.ts ('tax fields are stored apart')</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Tax category and tax cost stored on the asset for V4 (capital allowances); depreciation never reads them (architecture-tested); changing them changed no preview figure.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1928,9 +2000,9 @@
           <t>V2-M2</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1953,8 +2025,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/fixed-assets.test.ts ('the register at 31.12.2026 ... reconciles', 'an unregistered posting ... reconciling item')</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Per cost and accumulated-depreciation account at a date: register against ledger, with every posting the register neither made nor linked listed as a reconciling item; golden reconciles to the cent, a manual posting shows as a 250.00 difference.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3712,7 +3792,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ACCEPTED under the delegation 2026-10-18 (v2-m2-acceptance.md; CI 39159238749 on da32ffc)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3727,7 +3807,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 4.4; v2-m2-acceptance.md</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3739,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3994,7 +4074,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -4014,7 +4094,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -4044,7 +4124,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4055,7 +4135,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fd0f556</t>
+          <t>da32ffc</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4147,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39083312122</t>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39159238749</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4128,6 +4208,20 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v1.3 (2026-10-18, V2-M2, DEC-057/058): fixed assets built. Missing -&gt; Implemented: V2-MOD-03, V2-MOD-04, V2-FA-01..08. Golden review of V2-M1 by Shoaib recorded (DEC-057); V2-TEST-01 stays Partially.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v1.3a (2026-10-18): V2-M2 evidence recorded (CI 39159238749 and CodeQL 39159238888 green on da32ffc; clean clone 2047 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan history" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V2 matrix'!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V2 matrix'!$A$1:$K$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1054,9 +1054,9 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1079,8 +1079,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m3a-adjustments.json (docs/architecture/v2-m3a-golden-workings.xlsx recomputes all 51 figures independently: 0 differences); tests/api/year-end.test.ts; tests/platform/year-end.test.ts; tests/db/year-end.test.ts</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Accruals and accrued income post at the date with their reversal on the next day (ACCRUAL, ACCRUAL_AUTO_REVERSAL), which must fall in an open period. Evidence documents are linked to the item; a wrong accrual is cancelled by mirrors of both journals. Listed in the year-end register and reconciled to the ledger.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1103,9 +1111,9 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1128,8 +1136,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m3a-adjustments.json (docs/architecture/v2-m3a-golden-workings.xlsx recomputes all 51 figures independently: 0 differences); tests/api/year-end.test.ts; tests/platform/year-end.test.ts; tests/db/year-end.test.ts</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Prepayments are set up from the expense account (posted) or linked to the payment that carries them, and released by release runs, straight line by day or by month. The balance reconciles to the ledger by account; unregistered postings are listed.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1152,9 +1168,9 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1177,8 +1193,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m3a-adjustments.json (docs/architecture/v2-m3a-golden-workings.xlsx recomputes all 51 figures independently: 0 differences); tests/api/year-end.test.ts; tests/platform/year-end.test.ts; tests/db/year-end.test.ts</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>A provision records its accounts and basis. Movements are made, used and released in date order and never take the balance below zero (service and database). The movement report gives opening, made, used, released and closing; the balance reconciles to the ledger. Discounting is not covered (DEC-059).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1201,9 +1225,9 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1226,28 +1250,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m3a-adjustments.json (docs/architecture/v2-m3a-golden-workings.xlsx recomputes all 51 figures independently: 0 differences); tests/api/year-end.test.ts; tests/platform/year-end.test.ts; tests/db/year-end.test.ts</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Deferred income is set up from the income account or linked, and released by release runs. The balance reconciles to the ledger.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-09</t>
+          <t>V2-YEC-01</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>V2 Modules</t>
+          <t>v2-proposal section 4 (V2-M3)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Director/shareholder balances</t>
+          <t>Year-end closing journal to retained earnings</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>V2-M4</t>
+          <t>V2-M3</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1262,12 +1294,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>V2-M1</t>
+          <t>DEC-059</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Director loan accounts per person with movements and the year-end balance; overdrawn balances and large movements flagged.</t>
+          <t>The year's income and expense balances are closed to the retained-earnings account by one journal at the year end, reversible only by its mirror; every P&amp;L figure (management P&amp;L, statutory preview, FX report) excludes closing journals, and balance sheets include them, so statements reconcile before and after the close.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1276,12 +1308,16 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Added 2026-10-18 from the approved plan (DEC-059): the closing journal was in V2-M3's approved scope but had no matrix row. Built in V2-M3b.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-10</t>
+          <t>V2-MOD-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1291,7 +1327,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Related parties</t>
+          <t>Director/shareholder balances</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1316,7 +1352,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Related parties recorded with relationship and transactions for the year, available to the notes.</t>
+          <t>Director loan accounts per person with movements and the year-end balance; overdrawn balances and large movements flagged.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1330,7 +1366,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-11</t>
+          <t>V2-MOD-10</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1340,32 +1376,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Comparative periods</t>
+          <t>Related parties</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>V2-M4</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>V2-M1</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Engineering (build); qualified accountant (rules)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>V2-M1</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Statements show the prior financial year on the same standard version, from the ledger.</t>
+          <t>Related parties recorded with relationship and transactions for the year, available to the notes.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1373,21 +1409,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>tests/api/statutory.test.ts (golden comparative 2025 on the 2026 version)</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>The prior framework year (else the twelve months before) on the current year's version, from journal lines.</t>
-        </is>
-      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-12</t>
+          <t>V2-MOD-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1397,17 +1425,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Comparative periods</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>V2-M5</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>V2-M1</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1422,7 +1450,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Notes rendered from verified disclosure rules with their figures from the ledger; required notes per size present.</t>
+          <t>Statements show the prior financial year on the same standard version, from the ledger.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1430,13 +1458,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/statutory.test.ts (golden comparative 2025 on the 2026 version)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>The prior framework year (else the twelve months before) on the current year's version, from journal lines.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-13</t>
+          <t>V2-MOD-12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1446,7 +1482,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Statutory statements</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1471,7 +1507,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>P&amp;L and balance sheet in the layout of the chosen standard version; cash flow where the standard requires it.</t>
+          <t>Notes rendered from verified disclosure rules with their figures from the ledger; required notes per size present.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1485,7 +1521,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-14</t>
+          <t>V2-MOD-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1495,12 +1531,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Review checklist</t>
+          <t>Statutory statements</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>V2-M6</t>
+          <t>V2-M5</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1510,7 +1546,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (build); qualified accountant (rules)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1520,7 +1556,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Checklist built from the review flags (V2-RC rows) with sign-off per item.</t>
+          <t>P&amp;L and balance sheet in the layout of the chosen standard version; cash flow where the standard requires it.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1534,7 +1570,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>V2-MOD-15</t>
+          <t>V2-MOD-14</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1544,7 +1580,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Accounts approval</t>
+          <t>Review checklist</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1569,7 +1605,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Partner review then client approval recorded with person and time; approval locks the year's framework and figures.</t>
+          <t>Checklist built from the review flags (V2-RC rows) with sign-off per item.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1583,27 +1619,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-01</t>
+          <t>V2-MOD-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>V2 Fixed Assets</t>
+          <t>V2 Modules</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Additions</t>
+          <t>Accounts approval</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>V2-M2</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
+          <t>V2-M6</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,7 +1654,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Implemented with service, database and API tests and a hand-calculated golden example; postings through the PostingService with the five test categories; register reconciles to the cost and depreciation accounts to the cent.</t>
+          <t>Partner review then client approval recorded with person and time; approval locks the year's framework and figures.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1626,21 +1662,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Three kinds: POSTED (Dr cost / Cr a non-control offset), LINKED to the posting that already carries the cost (over-linking refused), TAKE_ON with accumulated depreciation. Reversal of a POSTED addition before any depreciation (VOID).</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-02</t>
+          <t>V2-FA-01</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1650,7 +1678,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Disposals (with gain or loss)</t>
+          <t>Additions</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1690,14 +1718,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Full disposals: catch-up to the disposal date, cost and accumulated depreciation removed, carrying amount and proceeds on the class disposal account; gain or loss = proceeds - carrying amount. Reversed by its mirror while no later run is live. Partial disposals are out of scope (DEC-058).</t>
+          <t>Three kinds: POSTED (Dr cost / Cr a non-control offset), LINKED to the posting that already carries the cost (over-linking refused), TAKE_ON with accumulated depreciation. Reversal of a POSTED addition before any depreciation (VOID).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-03</t>
+          <t>V2-FA-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1707,7 +1735,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Depreciation methods (straight line, reducing balance)</t>
+          <t>Disposals (with gain or loss)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1742,19 +1770,19 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>packages/accounting/src/depreciation-math.ts; tests/unit/depreciation-math.test.ts; tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Straight line and reducing balance, DAILY or MONTHLY convention; exact decimals; each charge = cumulative due (rounded half-up) - charged, so rounding never drifts.</t>
+          <t>Full disposals: catch-up to the disposal date, cost and accumulated depreciation removed, carrying amount and proceeds on the class disposal account; gain or loss = proceeds - carrying amount. Reversed by its mirror while no later run is live. Partial disposals are out of scope (DEC-058).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-04</t>
+          <t>V2-FA-03</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1764,7 +1792,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Useful lives</t>
+          <t>Depreciation methods (straight line, reducing balance)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1799,19 +1827,19 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
+          <t>packages/accounting/src/depreciation-math.ts; tests/unit/depreciation-math.test.ts; tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Life in months per class default or per asset; for a take-on, the remaining life; changed prospectively by a change of estimate (append-only bases).</t>
+          <t>Straight line and reducing balance, DAILY or MONTHLY convention; exact decimals; each charge = cumulative due (rounded half-up) - charged, so rounding never drifts.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-05</t>
+          <t>V2-FA-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1821,7 +1849,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Residual value</t>
+          <t>Useful lives</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1861,14 +1889,14 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Residual per asset (class default as a percentage of cost); straight line depreciates to it exactly; reducing balance never goes below it.</t>
+          <t>Life in months per class default or per asset; for a take-on, the remaining life; changed prospectively by a change of estimate (append-only bases).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-06</t>
+          <t>V2-FA-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1878,7 +1906,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Asset classes</t>
+          <t>Residual value</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1913,19 +1941,19 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>migration 20260120000000_v2_fixed_assets; tests/db/fixed-assets.test.ts ('classes'); tests/api/fixed-assets.test.ts ('classes name four accounts ...')</t>
+          <t>tests/golden/v2-m2-fixed-assets.json (hand figures; docs/architecture/v2-m2-golden-workings.xlsx recomputes all 37 independently: 0 differences); tests/api/fixed-assets.test.ts; tests/platform/fixed-assets.test.ts; tests/db/fixed-assets.test.ts</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>A class holds the four non-control accounts of the right type and subtype (database trigger) and the defaults for new assets; its code and accounts never move.</t>
+          <t>Residual per asset (class default as a percentage of cost); straight line depreciates to it exactly; reducing balance never goes below it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-07</t>
+          <t>V2-FA-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1935,7 +1963,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tax vs accounting treatment kept apart</t>
+          <t>Asset classes</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1965,24 +1993,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Capital allowances computations (V4)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>tests/unit/architecture.test.ts ('depreciation never reads the tax fields'); tests/api/fixed-assets.test.ts ('tax fields are stored apart')</t>
+          <t>migration 20260120000000_v2_fixed_assets; tests/db/fixed-assets.test.ts ('classes'); tests/api/fixed-assets.test.ts ('classes name four accounts ...')</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Tax category and tax cost stored on the asset for V4 (capital allowances); depreciation never reads them (architecture-tested); changing them changed no preview figure.</t>
+          <t>A class holds the four non-control accounts of the right type and subtype (database trigger) and the defaults for new assets; its code and accounts never move.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>V2-FA-08</t>
+          <t>V2-FA-07</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1992,7 +2020,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Reconciliation of the register to the ledger</t>
+          <t>Tax vs accounting treatment kept apart</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2022,44 +2050,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Capital allowances computations (V4)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>tests/api/fixed-assets.test.ts ('the register at 31.12.2026 ... reconciles', 'an unregistered posting ... reconciling item')</t>
+          <t>tests/unit/architecture.test.ts ('depreciation never reads the tax fields'); tests/api/fixed-assets.test.ts ('tax fields are stored apart')</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Per cost and accumulated-depreciation account at a date: register against ledger, with every posting the register neither made nor linked listed as a reconciling item; golden reconciles to the cent, a manual posting shows as a 250.00 difference.</t>
+          <t>Tax category and tax cost stored on the asset for V4 (capital allowances); depreciation never reads them (architecture-tested); changing them changed no preview figure.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-01</t>
+          <t>V2-FA-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>V2 Year-End Workflow</t>
+          <t>V2 Fixed Assets</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Lock/confirm period</t>
+          <t>Reconciliation of the register to the ledger</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>V2-M6</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>V2-M2</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2069,12 +2097,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>V2-M1..M5</t>
+          <t>V2-M1</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>The step reads its status from the existing control (V1 reconciliation sign-off, ageing, VAT reconciliation, alerts, V2 registers), records the reviewer's sign-off with time and notes, and blocks the next step where the specification requires it.</t>
+          <t>Implemented with service, database and API tests and a hand-calculated golden example; postings through the PostingService with the five test categories; register reconciles to the cost and depreciation accounts to the cent.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2082,13 +2110,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>tests/api/fixed-assets.test.ts ('the register at 31.12.2026 ... reconciles', 'an unregistered posting ... reconciling item')</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Per cost and accumulated-depreciation account at a date: register against ledger, with every posting the register neither made nor linked listed as a reconciling item; golden reconciles to the cent, a manual posting shows as a 250.00 difference.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-02</t>
+          <t>V2-YE-01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2098,7 +2134,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Bank reconciliation</t>
+          <t>Lock/confirm period</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2137,7 +2173,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-03</t>
+          <t>V2-YE-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2147,7 +2183,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Receivables review</t>
+          <t>Bank reconciliation</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2186,7 +2222,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-04</t>
+          <t>V2-YE-03</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2196,7 +2232,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Payables review</t>
+          <t>Receivables review</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2235,7 +2271,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-05</t>
+          <t>V2-YE-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2245,7 +2281,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fixed asset review</t>
+          <t>Payables review</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2284,7 +2320,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-06</t>
+          <t>V2-YE-05</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2294,7 +2330,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Accrual/prepayment review</t>
+          <t>Fixed asset review</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2333,7 +2369,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-07</t>
+          <t>V2-YE-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2343,7 +2379,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Director balances</t>
+          <t>Accrual/prepayment review</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2382,7 +2418,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-08</t>
+          <t>V2-YE-07</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2392,7 +2428,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VAT reconciliation</t>
+          <t>Director balances</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2431,7 +2467,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-09</t>
+          <t>V2-YE-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2441,7 +2477,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Suspense clearance</t>
+          <t>VAT reconciliation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2480,7 +2516,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-10</t>
+          <t>V2-YE-09</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2490,7 +2526,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Review adjustments</t>
+          <t>Suspense clearance</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2529,7 +2565,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-11</t>
+          <t>V2-YE-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2539,7 +2575,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Generate accounts</t>
+          <t>Review adjustments</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2578,7 +2614,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-12</t>
+          <t>V2-YE-11</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2588,7 +2624,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Partner review</t>
+          <t>Generate accounts</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2627,7 +2663,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-13</t>
+          <t>V2-YE-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2637,7 +2673,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Client approval</t>
+          <t>Partner review</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2676,7 +2712,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>V2-YE-14</t>
+          <t>V2-YE-13</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2686,7 +2722,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Filing-ready package</t>
+          <t>Client approval</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2716,7 +2752,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>iXBRL and Companies House filing (V3)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -2725,22 +2761,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-01</t>
+          <t>V2-YE-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>V2 Accounts Output</t>
+          <t>V2 Year-End Workflow</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Profit and loss</t>
+          <t>Filing-ready package</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>V2-M5</t>
+          <t>V2-M6</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2750,22 +2786,22 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Engineering (build); qualified accountant (rules)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>V2-M1</t>
+          <t>V2-M1..M5</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Produced from the ledger through the verified framework and matched to the golden output to the cent.</t>
+          <t>The step reads its status from the existing control (V1 reconciliation sign-off, ageing, VAT reconciliation, alerts, V2 registers), records the reviewer's sign-off with time and notes, and blocks the next step where the specification requires it.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>iXBRL and Companies House filing (V3)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2774,7 +2810,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-02</t>
+          <t>V2-OUT-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2784,7 +2820,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Balance sheet</t>
+          <t>Profit and loss</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2823,7 +2859,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-03</t>
+          <t>V2-OUT-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2833,7 +2869,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Cash flow where applicable</t>
+          <t>Balance sheet</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2872,7 +2908,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-04</t>
+          <t>V2-OUT-03</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2882,7 +2918,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Cash flow where applicable</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2921,7 +2957,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-05</t>
+          <t>V2-OUT-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2931,7 +2967,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Accounting policies</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2970,7 +3006,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-06</t>
+          <t>V2-OUT-05</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2980,29 +3016,29 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Comparatives</t>
+          <t>Accounting policies</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>V2-M5</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified accountant (rules)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
           <t>V2-M1</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Engineering (build); qualified accountant (rules)</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>V2-M1</t>
-        </is>
-      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Produced from the ledger through the verified framework and matched to the golden output to the cent.</t>
@@ -3013,21 +3049,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts ('reproduces the hand-written P&amp;L and balance sheet to the cent, with the comparative')</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Matched to the cent through a verified synthetic version (synthetic layout, not a real standard).</t>
-        </is>
-      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>V2-OUT-07</t>
+          <t>V2-OUT-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3037,17 +3065,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Directors/reporting sections where applicable</t>
+          <t>Comparatives</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>V2-M5</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>V2-M1</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3070,28 +3098,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts ('reproduces the hand-written P&amp;L and balance sheet to the cent, with the comparative')</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Matched to the cent through a verified synthetic version (synthetic layout, not a real standard).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-01</t>
+          <t>V2-OUT-07</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>V2 Review Controls</t>
+          <t>V2 Accounts Output</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Unexplained movements</t>
+          <t>Directors/reporting sections where applicable</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>V2-M6</t>
+          <t>V2-M5</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3101,17 +3137,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (build); qualified accountant (rules)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>V1-M8 alerts, V2-M2..M4</t>
+          <t>V2-M1</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Raised on the year-end review with its figures and drill-down, thresholds as data, cleared or explained with a reason by a named reviewer.</t>
+          <t>Produced from the ledger through the verified framework and matched to the golden output to the cent.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3125,7 +3161,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-02</t>
+          <t>V2-RC-01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3135,7 +3171,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Material changes</t>
+          <t>Unexplained movements</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3174,7 +3210,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-03</t>
+          <t>V2-RC-02</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3184,7 +3220,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Unusual balances</t>
+          <t>Material changes</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3223,7 +3259,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-04</t>
+          <t>V2-RC-03</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3233,7 +3269,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Negative balances</t>
+          <t>Unusual balances</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3272,7 +3308,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-05</t>
+          <t>V2-RC-04</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3282,7 +3318,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Old receivables/payables</t>
+          <t>Negative balances</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3321,7 +3357,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-06</t>
+          <t>V2-RC-05</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3331,7 +3367,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Director loan movements</t>
+          <t>Old receivables/payables</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3370,7 +3406,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-07</t>
+          <t>V2-RC-06</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3380,7 +3416,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Suspense</t>
+          <t>Director loan movements</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3419,7 +3455,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-08</t>
+          <t>V2-RC-07</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3429,7 +3465,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Unreconciled bank</t>
+          <t>Suspense</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3468,7 +3504,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>V2-RC-09</t>
+          <t>V2-RC-08</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3478,7 +3514,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Missing supporting evidence</t>
+          <t>Unreconciled bank</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3517,42 +3553,42 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>V2-TEST-01</t>
+          <t>V2-RC-09</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>V2 Tests</t>
+          <t>V2 Review Controls</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Golden trial balances and expected statutory outputs</t>
+          <t>Missing supporting evidence</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>V2-M1</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>V2-M6</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Engineering (build); qualified accountant (rules)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>DEC-054</t>
+          <t>V1-M8 alerts, V2-M2..M4</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Each scenario's expected statements and notes are hand-written data in tests/golden/ and matched to the cent; the named accountant reviews them before verifying the rules they exercise.</t>
+          <t>Raised on the year-end review with its figures and drill-down, thresholds as data, cleared or explained with a reason by a named reviewer.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3560,68 +3596,117 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified.</t>
-        </is>
-      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>V2-TEST-01</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>V2 Tests</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Golden trial balances and expected statutory outputs</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>V2-M1</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified accountant (rules)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>DEC-054</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Each scenario's expected statements and notes are hand-written data in tests/golden/ and matched to the cent; the named accountant reviews them before verifying the rules they exercise.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>V2-DOD-01</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Manifest definition of done</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>V2 workflows usable in screens</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>V2-M7</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>V2-M1..M6</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Every V2 module has screens behind accounts.production, real-browser tested (DEC-050 pattern).</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K61"/>
+  <autoFilter ref="A1:K62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3835,7 +3920,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>SPLIT (DEC-059): V2-M3a adjustments BUILT 2026-10-18 (v2-m3a-acceptance.md); V2-M3b closing journal next</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3850,7 +3935,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 5.3; v2-m3a-acceptance.md (V2-M3a)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3859,10 +3944,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4074,7 +4159,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4094,7 +4179,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -4114,7 +4199,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -4124,7 +4209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4133,11 +4218,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>da32ffc</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4145,11 +4226,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39159238749</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4174,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4222,6 +4299,13 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v1.4 (2026-10-18, V2-M3a, DEC-059): year-end adjustments built. Missing -&gt; Implemented: V2-MOD-05..08. Row added: V2-YEC-01, the year-end closing journal, which was in the approved V2-M3 scope but missing from the matrix (61 rows).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-059): V2-M3a adjustments BUILT 2026-10-18 (v2-m3a-acceptance.md); V2-M3b closing journal next</t>
+          <t>SPLIT (DEC-059): V2-M3a adjustments ACCEPTED under the delegation 2026-10-18 (v2-m3a-acceptance.md; CI 39178258465 on f735149); V2-M3b closing journal next</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4218,7 +4218,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>f735149</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4226,7 +4230,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39178258465</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4236,7 +4244,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4306,6 +4314,13 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v1.4a (2026-10-18): V2-M3a evidence recorded (CI 39178258465 and CodeQL 39178258477 green on f735149; clean clone 2091 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1282,9 +1282,9 @@
           <t>V2-M3</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1307,10 +1307,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m3b-close.json (docs/architecture/v2-m3b-golden-workings.xlsx recomputes all 152 figures independently: 0 differences); tests/api/year-end-close.test.ts; tests/platform/year-end-close.test.ts; tests/db/year-end-close.test.ts; tests/api/statutory.test.ts (preview unchanged by closes)</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-10-18 from the approved plan (DEC-059): the closing journal was in V2-M3's approved scope but had no matrix row. Built in V2-M3b.</t>
+          <t>Added 2026-10-18 from the approved plan (DEC-059). Built in V2-M3b (DEC-060): one closing journal per financial year (aligned to accounting periods, at most 18 months, never overlapping a live close) moves every income and expense balance of the year to retained earnings; while it is live the PostingService and the database refuse income and expense dated in the year; it is corrected only by its mirror. The management P&amp;L, the balance sheet lines, the statutory preview and the FX report leave closing journals out and read the same before and after a close; the trial balance and the balance sheet's trial-balance proof include them.</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3924,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-059): V2-M3a adjustments ACCEPTED under the delegation 2026-10-18 (v2-m3a-acceptance.md; CI 39178258465 on f735149); V2-M3b closing journal next</t>
+          <t>SPLIT (DEC-059): V2-M3a adjustments ACCEPTED under the delegation 2026-10-18 (v2-m3a-acceptance.md; CI 39178258465 on f735149); V2-M3b closing journal BUILT 2026-10-19 (v2-m3b-acceptance.md)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3935,7 +3939,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5.3; v2-m3a-acceptance.md (V2-M3a)</t>
+          <t>v2-plan.md sections 5.3 and 5b.4; v2-m3a-acceptance.md (V2-M3a); v2-m3b-acceptance.md (V2-M3b)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3947,7 +3951,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4159,7 +4163,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4179,7 +4183,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -4218,11 +4222,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>f735149</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4230,11 +4230,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39178258465</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4259,7 +4255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4321,6 +4317,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v1.5 (2026-10-19, V2-M3b, DEC-060): year-end closing journal built. Missing -&gt; Implemented: V2-YEC-01.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-059): V2-M3a adjustments ACCEPTED under the delegation 2026-10-18 (v2-m3a-acceptance.md; CI 39178258465 on f735149); V2-M3b closing journal BUILT 2026-10-19 (v2-m3b-acceptance.md)</t>
+          <t>ACCEPTED under the delegation (DEC-059 split): V2-M3a 2026-10-18 (v2-m3a-acceptance.md; CI 39178258465 on f735149); V2-M3b 2026-10-19 (v2-m3b-acceptance.md; CI 39181318428 on 5ab27b8)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4222,7 +4222,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5ab27b8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4230,7 +4234,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39181318428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4255,7 +4263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4324,6 +4332,13 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v1.5a (2026-10-19): V2-M3b evidence recorded (CI 39181318428 and CodeQL 39181318430 green on 5ab27b8; clean clone 2117 tests, e2e 21/21, OpenAPI drift 0). Milestone V2-M3 accepted.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1339,9 +1339,9 @@
           <t>V2-M4</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1364,8 +1364,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m4-directors.json (docs/architecture/v2-m4-golden-workings.xlsx recomputes all 79 figures independently: 0 differences); tests/api/directors.test.ts; tests/platform/directors.test.ts; tests/db/directors.test.ts; tests/unit/directors.test.ts</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M4 (DEC-062): a loan account per director or shareholder on a dedicated non-control ledger account (a director needs a DIRECTOR appointment); statements with every movement, its category and running balance, the lowest day-end balance and days overdrawn; review flags (overdrawn at the end and in the period; large movements and overdrawn beyond the firm's versioned thresholds, reported as not evaluated when unset). Reads the ledger only; no legal threshold is encoded.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1388,9 +1396,9 @@
           <t>V2-M4</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1413,8 +1421,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m4-directors.json (docs/architecture/v2-m4-golden-workings.xlsx recomputes all 79 figures independently: 0 differences); tests/api/directors.test.ts; tests/platform/directors.test.ts; tests/db/directors.test.ts; tests/unit/directors.test.ts</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M4 (DEC-062): a related-party register (counterparty, relationship, description, from and to dates; ended once) and a report per party for any range: sales and purchases net of VAT from its documents, cash paid and received from its cash transactions, owed by and owed to at the end from the control accounts, and its loan accounts, each with the journals behind it, as the input for the related-party note (V2-M5).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3967,7 +3983,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>BUILT 2026-10-19 (v2-m4-acceptance.md)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3982,7 +3998,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 5c.3; v2-m4-acceptance.md</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3994,7 +4010,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4163,7 +4179,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4183,7 +4199,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -4222,11 +4238,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>5ab27b8</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4234,11 +4246,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39181318428</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4263,7 +4271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4339,6 +4347,13 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v1.6 (2026-10-19, V2-M4, DEC-061/062): DEC-061 records the review of the V2-M2, V2-M3a and V2-M3b golden workings by Shoaib (no row changes status from it). Director and shareholder loan accounts and related parties built. Missing -&gt; Implemented: V2-MOD-09, V2-MOD-10.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3983,7 +3983,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-19 (v2-m4-acceptance.md)</t>
+          <t>ACCEPTED under the delegation 2026-10-19 (v2-m4-acceptance.md; CI 39251457210 on 87c8956)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4238,7 +4238,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>87c8956</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4246,7 +4250,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39251457210</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4271,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4354,6 +4362,13 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v1.6a (2026-10-19): V2-M4 evidence recorded (CI 39251457210 and CodeQL 39251456129 green on 87c8956; clean clone 2146 tests, e2e 21/21, OpenAPI drift 0). A V1-M9a screen defect found by the first clean clone (a stale answer overwriting a newer one) was fixed in 87c8956.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1510,9 +1510,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1535,8 +1535,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Notes rendered by V2-M5a (DEC-063) from the version's wording (disclosure rules with section, order, template and omit-when-empty; verified and frozen with the version) and facts from the ledger (fixed-asset movements), the registers (provisions, advances to directors, related parties) and the preparer (employees, approval, company wording); a rule applies to the sizes it lists; missing facts are reported and keep the document incomplete. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1559,9 +1567,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1584,8 +1592,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Statements in the layout of the chosen version (V2-M1 preview, now part of the accounts document with comparatives, V2-M5a). The cash flow statement where the standard requires it is V2-M5b. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2848,9 +2864,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2873,8 +2889,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>The P&amp;L of the accounts document (V2-M5a) through the verified version, with the comparative, matched to the golden output to the cent (v2-m1 and v2-m5a goldens). Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2897,9 +2921,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2922,8 +2946,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden)</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>The balance sheet of the accounts document (V2-M5a) through the verified version, with the comparative, matched to the golden output to the cent (v2-m1 and v2-m5a goldens). Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2995,9 +3027,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3020,8 +3052,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Notes in the accounts document (V2-M5a): text and tables rendered exactly as the golden output. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3044,9 +3084,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3069,8 +3109,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Accounting policies are the POLICIES section of the accounts document (V2-M5a), rendered from the version's wording exactly as the golden output. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3150,9 +3198,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3175,8 +3223,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Directors' report and balance-sheet statements are sections of the accounts document (V2-M5a), applied by entity size (a small-company section is left out for a micro-entity in the golden), with the directors and the approval facts. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4026,7 +4082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>SPLIT (DEC-063): V2-M5a the accounts document BUILT 2026-10-19 (v2-m5a-acceptance.md); V2-M5b the size test and the cash flow statement next</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4041,7 +4097,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 5d.3; v2-m5a-acceptance.md (V2-M5a)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4053,7 +4109,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -4179,7 +4235,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -4189,7 +4245,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4199,7 +4255,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -4238,11 +4294,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>87c8956</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4250,11 +4302,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39251457210</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4279,7 +4327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4369,6 +4417,13 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v1.7 (2026-10-19, V2-M5a, DEC-063): V2-M5 split; the accounts document built. Missing -&gt; Implemented: V2-MOD-12, V2-OUT-01, V2-OUT-02, V2-OUT-04, V2-OUT-05, V2-OUT-07. Missing -&gt; Partially: V2-MOD-13 (cash flow in V2-M5b). Mechanism proven on synthetic verified wording only; real standard wording remains the named accountant's (DEC-052).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-063): V2-M5a the accounts document BUILT 2026-10-19 (v2-m5a-acceptance.md); V2-M5b the size test and the cash flow statement next</t>
+          <t>SPLIT (DEC-063): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test and the cash flow statement next</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4294,7 +4294,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1492ff6</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4302,7 +4306,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39271179477</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4327,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4424,6 +4432,13 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v1.7a (2026-10-19): V2-M5a evidence recorded (CI 39271179477 and CodeQL 39271179462 green on 1492ff6; clean clone 2163 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4294,11 +4294,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1492ff6</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4306,11 +4302,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39271179477</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4335,7 +4327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4439,6 +4431,13 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v1.8 (2026-10-19, DEC-064): at the product owner's instruction engineering drafted FRS 105 (micro) and FRS 102 Section 1A (small) wording packs (content/standards/drafts), importable through the API as UNVERIFIED versions; review workbook v2-draft-wording-review.xlsx. No row changes status: the drafts are unverified and were not checked against the source text (DEC-052).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4294,7 +4294,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>d08ecb3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4302,7 +4306,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39288936490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4327,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4438,6 +4446,13 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v1.8a (2026-10-19): draft wording packs evidence recorded (CI 39288936490 and CodeQL 39288936669 green on d08ecb3; clean clone 2175 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1594,12 +1594,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden)</t>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden); tests/golden/v2-m5b-size.json (docs/architecture/v2-m5b-golden-workings.xlsx recomputes every figure, limit, condition and status independently: 139 checks, 0 differences); tests/api/size-test.test.ts; tests/unit/size-test.test.ts; tests/db/size-test.test.ts</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Statements in the layout of the chosen version (V2-M1 preview, now part of the accounts document with comparatives, V2-M5a). The cash flow statement where the standard requires it is V2-M5b. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+          <t>Statements in the layout of the chosen version (V2-M1 preview, now part of the accounts document with comparatives, V2-M5a). The size test that decides which statements and notes a year may use is built in V2-M5b (DEC-066): company-law thresholds as sourced data verified by a second person, the two-or-more-of-three conditions, the two-consecutive-years rule, short years, and whether the chosen entity size fits; proven on synthetic limits, and the draft UK thresholds are unverified. The cash flow statement where the standard requires it is V2-M5c. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
         </is>
       </c>
     </row>
@@ -3723,12 +3723,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts</t>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified.</t>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M5b, the last being the size test over four years with two threshold sets); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M5b goldens.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-063): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test and the cash flow statement next</t>
+          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test built 2026-10-20 (v2-m5b-acceptance.md); V2-M5c the cash flow statement next</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5d.3; v2-m5a-acceptance.md (V2-M5a)</t>
+          <t>v2-plan.md sections 5d.3 and 5f.5; v2-m5a-acceptance.md (V2-M5a); v2-m5b-acceptance.md (V2-M5b)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4294,11 +4294,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>d08ecb3</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4306,11 +4302,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39288936490</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4320,7 +4312,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4453,6 +4445,13 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v1.9 (2026-10-20, V2-M5b, DEC-065/066): DEC-065 records the product owner's read of the draft wording packs (no verdicts; nothing verified). DEC-066 splits V2-M5 again (V2-M5c the cash flow statement) and builds the size test: threshold sets as sourced data verified by a second person, a version's turnover line, two facts for the earliest year, the size-test endpoint; draft UK thresholds importable as UNVERIFIED sets. No row changes status: V2-MOD-13 stays Partially implemented until the cash flow statement; V2-MOD-13 and V2-TEST-01 gain evidence.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test built 2026-10-20 (v2-m5b-acceptance.md); V2-M5c the cash flow statement next</t>
+          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test ACCEPTED under the delegation 2026-10-20 (v2-m5b-acceptance.md; CI 39362598139 on 2277775); V2-M5c the cash flow statement next</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4294,7 +4294,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2277775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4302,7 +4306,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39362598139</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4327,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4452,6 +4460,13 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v1.9a (2026-10-20): V2-M5b evidence recorded (CI 39362598139 and CodeQL 39362598131 green on 2277775; clean clone 2204 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1567,9 +1567,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden); tests/golden/v2-m5b-size.json (docs/architecture/v2-m5b-golden-workings.xlsx recomputes every figure, limit, condition and status independently: 139 checks, 0 differences); tests/api/size-test.test.ts; tests/unit/size-test.test.ts; tests/db/size-test.test.ts</t>
+          <t>tests/golden/v2-m5a-document.json (docs/architecture/v2-m5a-golden-workings.xlsx recomputes every figure, table and sentence independently: 62 checks, 0 differences); tests/api/accounts-document.test.ts; tests/unit/accounts-document.test.ts; tests/db/accounts-document.test.ts; tests/api/statutory.test.ts (V2-M1 golden); tests/golden/v2-m5b-size.json (docs/architecture/v2-m5b-golden-workings.xlsx recomputes every figure, limit, condition and status independently: 139 checks, 0 differences); tests/api/size-test.test.ts; tests/unit/size-test.test.ts; tests/db/size-test.test.ts; tests/golden/v2-m5c-cash-flow.json (docs/architecture/v2-m5c-golden-workings.xlsx recomputes every line, total and cash balance independently, with a direct-method check: 106 checks, 0 differences); tests/api/cash-flow.test.ts; tests/unit/cash-flow.test.ts; tests/db/cash-flow.test.ts</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Statements in the layout of the chosen version (V2-M1 preview, now part of the accounts document with comparatives, V2-M5a). The size test that decides which statements and notes a year may use is built in V2-M5b (DEC-066): company-law thresholds as sourced data verified by a second person, the two-or-more-of-three conditions, the two-consecutive-years rule, short years, and whether the chosen entity size fits; proven on synthetic limits, and the draft UK thresholds are unverified. The cash flow statement where the standard requires it is V2-M5c. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
+          <t>Statements in the layout of the chosen version (V2-M1 preview, now part of the accounts document with comparatives, V2-M5a). The size test that decides which statements and notes a year may use is built in V2-M5b (DEC-066): company-law thresholds as sourced data verified by a second person, the two-or-more-of-three conditions, the two-consecutive-years rule, short years, and whether the chosen entity size fits; proven on synthetic limits, and the draft UK thresholds are unverified. The cash flow statement is built in V2-M5c (DEC-067) and joins the statements for the sizes the version lists. Proven on a verified synthetic version with synthetic wording; no real FRS 105, FRS 102 or Companies Act wording is entered or verified (DEC-052): that is for the named accountant.</t>
         </is>
       </c>
     </row>
@@ -2978,9 +2978,9 @@
           <t>V2-M5</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3003,8 +3003,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m5c-cash-flow.json (docs/architecture/v2-m5c-golden-workings.xlsx recomputes every line, total and cash balance independently, with a direct-method check: 106 checks, 0 differences); tests/api/cash-flow.test.ts; tests/unit/cash-flow.test.ts; tests/db/cash-flow.test.ts</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M5c (DEC-067): the cash flow statement by the indirect method, from the ledger through the version's cash-flow classes, map and captions (version content, verified with it). Operating, investing and financing sections with gross receipts and payments where a class asks for them, the comparative year, the accounts of each line, and a proof against the movement in cash; it joins the accounts document for the sizes the version lists. An account the map does not place is shown as unclassified and keeps the document incomplete. Proven on a verified synthetic version with synthetic classes and captions; no real FRS 102 Section 7 classification or caption is entered or verified (DEC-052): that is for the named accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3723,12 +3731,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M5b, the last being the size test over four years with two threshold sets); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M5b goldens.</t>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M5c, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M5c goldens.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4090,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED under the delegation 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test ACCEPTED under the delegation 2026-10-20 (v2-m5b-acceptance.md; CI 39362598139 on 2277775); V2-M5c the cash flow statement next</t>
+          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test ACCEPTED 2026-10-20 (v2-m5b-acceptance.md; CI 39362598139 on 2277775); V2-M5c the cash flow statement built 2026-10-20 (v2-m5c-acceptance.md), all under the delegation</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4097,7 +4105,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md sections 5d.3 and 5f.5; v2-m5a-acceptance.md (V2-M5a); v2-m5b-acceptance.md (V2-M5b)</t>
+          <t>v2-plan.md sections 5d.3, 5f.5 and 5g.4; v2-m5a-acceptance.md (V2-M5a); v2-m5b-acceptance.md (V2-M5b); v2-m5c-acceptance.md (V2-M5c)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4109,7 +4117,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -4235,7 +4243,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -4245,7 +4253,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -4255,7 +4263,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -4294,11 +4302,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2277775</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4306,11 +4310,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39362598139</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4467,6 +4467,13 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v2.0 (2026-10-20, V2-M5c, DEC-067): the cash flow statement built (indirect method from the ledger; classes, map and captions as version content verified with it). Missing -&gt; Implemented: V2-OUT-03. Partially -&gt; Implemented: V2-MOD-13. V2-TEST-01 gains the V2-M5c golden. Proven on synthetic content only; no real FRS 102 classification or caption is entered or verified (DEC-052).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4090,7 +4090,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-063, DEC-066): V2-M5a the accounts document ACCEPTED 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test ACCEPTED 2026-10-20 (v2-m5b-acceptance.md; CI 39362598139 on 2277775); V2-M5c the cash flow statement built 2026-10-20 (v2-m5c-acceptance.md), all under the delegation</t>
+          <t>ACCEPTED under the delegation (DEC-063, DEC-066 split): V2-M5a the accounts document 2026-10-19 (v2-m5a-acceptance.md; CI 39271179477 on 1492ff6); V2-M5b the size test 2026-10-20 (v2-m5b-acceptance.md; CI 39362598139 on 2277775); V2-M5c the cash flow statement 2026-10-20 (v2-m5c-acceptance.md; CI 39396072282 on 8fcee2c)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4302,7 +4302,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8fcee2c</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4310,7 +4314,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39396072282</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4335,7 +4343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4474,6 +4482,13 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v2.0a (2026-10-20): V2-M5c evidence recorded (CI 39396072282 and CodeQL 39396072207 green on 8fcee2c; clean clone 2225 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -1624,9 +1624,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1649,8 +1649,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M6a (DEC-068): the review checklist of a framework year lists the nine controls (V2-RC-01 to V2-RC-09), each CLEAR, OPEN, EXPLAINED, SIGNED_OFF or NOT_EVALUATED, with its flags, figures, drill-down and responses; sign-off per flag by a second person holding accounts:review; resolved flags keep their history; complete when every control is evaluated and every flag is signed off. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3263,9 +3271,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3288,8 +3296,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Manual and control-adjustment journals of the year at or above the firm's unexplained-movement setting, with the journal's figures and drill-down. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3312,9 +3328,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3337,8 +3353,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Statutory lines fed by accounts, and the retained profit, that move from the comparative by at least the firm's amount and percentage settings, with current, comparative, change and percentage. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3361,9 +3385,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3386,8 +3410,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L accounts whose net for the year is on the wrong side (income in debit, expense in credit), closing journals left out. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3410,9 +3442,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3435,8 +3467,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Asset accounts (other than accumulated depreciation) in credit and liability accounts in debit at the year end. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3459,9 +3499,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3484,8 +3524,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Customers and suppliers with amounts overdue beyond the firm's setting (30, 60 or 90 days) at the year end, from the V1 aged reports. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3508,9 +3556,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3533,8 +3581,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Director and shareholder loan accounts carrying any V2-M4 flag for the year (overdrawn at the end or in the period, large movements, overdrawn beyond the firm's threshold), with closing, lowest and days overdrawn. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3557,9 +3613,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3582,8 +3638,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Suspense accounts with a balance at the year end. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3606,9 +3670,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3631,8 +3695,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts in use at the year end without a signed reconciliation at the year end or with a difference, and bank ledger accounts with a balance but no bank account set up. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3655,9 +3727,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3680,8 +3752,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6a-review.json (docs/architecture/v2-m6a-golden-workings.xlsx recomputes every flag and figure independently: 38 checks, 0 differences); tests/api/review.test.ts; tests/unit/review.test.ts; tests/db/review.test.ts</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Manual and control-adjustment journals, approved purchase bills and cash payments of the year at or above the firm's evidence setting without a live evidence link to a document. Raised live by V2-M6a (DEC-068) on the review checklist of a framework year; settings are the firm's, versioned, and a control whose setting is not set is NOT_EVALUATED, never passed. Each flag is explained by a preparer (accounts:prepare) and signed off by a second person holding accounts:review; an explanation lapses when the figures change; the database repeats the second-person rule. Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3731,12 +3811,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json; tests/golden/v2-m6a-review.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M5c, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M5c goldens.</t>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M6a, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M6a goldens.</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4213,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist built 2026-10-21 (v2-m6a-acceptance.md); V2-M6b the 14-step year-end workflow and V2-M6c approval, locking and the filing-ready package next</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4148,7 +4228,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 5h.3; v2-m6a-acceptance.md (V2-M6a)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4160,7 +4240,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4243,7 +4323,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -4263,7 +4343,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -4302,11 +4382,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8fcee2c</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4314,11 +4390,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39396072282</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4328,7 +4400,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4489,6 +4561,13 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v2.1 (2026-10-21, V2-M6a, DEC-068): V2-M6 split; review flags and the review checklist built. Missing -&gt; Implemented: V2-RC-01 to V2-RC-09, V2-MOD-14. V2-TEST-01 gains the V2-M6a golden. Proven on synthetic data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist built 2026-10-21 (v2-m6a-acceptance.md); V2-M6b the 14-step year-end workflow and V2-M6c approval, locking and the filing-ready package next</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED under the delegation 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow and V2-M6c approval, locking and the filing-ready package next</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4382,7 +4382,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8646c7e</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4390,7 +4394,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39575388052</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4415,7 +4423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4568,6 +4576,13 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>v2.1a (2026-10-21): V2-M6a evidence recorded (CI 39575388052 and CodeQL 39575387880 green on 8646c7e; clean clone 2256 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -834,9 +834,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -859,8 +859,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M6b (DEC-069): the 14-step workflow of a framework year with each step's control read from an existing control, its dependencies, its state (LATER, DONE, LAPSED, BLOCKED, TODO, ATTENTION), its sign-offs and the current step; steps 1 to 11 work end to end. Partially: steps 12 to 14 (partner review, client approval, the filing-ready package) arrive with V2-M6c.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2186,9 +2194,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2211,8 +2219,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the bookkeeping cut-off: the year's periods cover it without gaps, no draft sales or purchase documents and no pending journal requests are dated in it (the periods are locked at approval, V2-M6c, because adjustments still post). Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2235,9 +2251,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2260,8 +2276,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is review control RC-08 (unreconciled bank) being clear or signed off. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2284,9 +2308,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2309,8 +2333,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the customer flags of RC-05 (old receivables from the V1 aged report) being none or signed off, with RC-05 evaluated. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2333,9 +2365,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2358,8 +2390,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the supplier flags of RC-05 (old payables from the V1 aged report) being none or signed off, with RC-05 evaluated. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2382,9 +2422,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2407,8 +2447,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the V2-M2 register reconciling to the ledger at the year end, with a live depreciation run as at the year end when an asset is in use. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2431,9 +2479,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2456,8 +2504,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the V2-M3a year-end register reconciling to the ledger at the year end. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2480,9 +2536,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2505,8 +2561,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is review control RC-06 (director loan movements) being clear or signed off. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2529,9 +2593,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2554,8 +2618,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the V1 VAT workpaper for the year having no unexplained reconciliation difference (not applicable when the company is not VAT registered). Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2578,9 +2650,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2603,8 +2675,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is review control RC-07 (suspense) being clear or signed off. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2627,9 +2707,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2652,8 +2732,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the V2-M6a review checklist being complete (every control evaluated, every flag signed off). Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2676,9 +2764,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2701,8 +2789,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>The step reads its status from an existing control: its control is the V2-M5 accounts document being complete and the V2-M5b size test verified and fitting the chosen size. Built in V2-M6b (DEC-069): the step shows its control (READY, ATTENTION with what needs doing, or NOT_APPLICABLE), records the preparer's sign-off with time, note and the control at the time, lapses when the control stops being ready, and is blocked until the steps it depends on are done (1 first; 2-9 after 1; 10 after 1-9; 11 after 10). Proven on synthetic data.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2751,7 +2847,11 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2800,7 +2900,11 @@
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2849,7 +2953,11 @@
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3811,12 +3919,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json; tests/golden/v2-m6a-review.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json; tests/golden/v2-m6a-review.json; tests/golden/v2-m6b-workflow.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M6a, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M6a goldens.</t>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M6b, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M6b goldens.</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4321,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED under the delegation 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow and V2-M6c approval, locking and the filing-ready package next</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow built 2026-10-21 (v2-m6b-acceptance.md); V2-M6c approval, locking and the filing-ready package next</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4228,7 +4336,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5h.3; v2-m6a-acceptance.md (V2-M6a)</t>
+          <t>v2-plan.md sections 5h.3 and 5i.4; v2-m6a-acceptance.md (V2-M6a); v2-m6b-acceptance.md (V2-M6b)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4240,7 +4348,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -4323,7 +4431,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -4333,7 +4441,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4343,7 +4451,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4382,11 +4490,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8646c7e</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4394,11 +4498,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39575388052</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4423,7 +4523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4583,6 +4683,13 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v2.2 (2026-10-21, V2-M6b, DEC-069): the 14-step year-end workflow built. Missing -&gt; Implemented: V2-YE-01 to V2-YE-11. Missing -&gt; Partially: V2-MOD-01 (steps 12-14 in V2-M6c). V2-TEST-01 gains the V2-M6b golden. Proven on synthetic data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow built 2026-10-21 (v2-m6b-acceptance.md); V2-M6c approval, locking and the filing-ready package next</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow ACCEPTED 2026-10-21 (v2-m6b-acceptance.md; CI 39595091384 on 9868fbc); V2-M6c approval, locking and the filing-ready package next</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4490,7 +4490,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9868fbc</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4498,7 +4502,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39595091384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4523,7 +4531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4690,6 +4698,13 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>v2.2a (2026-10-21): V2-M6b evidence recorded (CI 39595091384 and CodeQL 39595091437 green on 9868fbc; clean clone 2275 tests, e2e 21/21, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -720,9 +720,9 @@
           <t>V2-M1</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>tests/api/statutory.test.ts ('verification by a second person'); tests/db/reporting-framework.test.ts ('verification: once, by a person other than the author ...')</t>
+          <t>tests/api/statutory.test.ts ('verification by a second person'); tests/db/reporting-framework.test.ts ('verification: once, by a person other than the author ...'); tests/db/accounts-approval.test.ts ('the filing-ready package (V2-ARC-04) is refused under a version not verified by a second person ...'); tests/unit/accounts-approval.test.ts ('the package gate'); tests/api/accounts-approval.test.ts</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Built and tested: author cannot verify (service 403 and database CHECK), verified version and its content immutable (service 409 and database trigger), changes supersede, unverified previews carry verified=false and a PREVIEW ONLY notice. Remaining: the filing-ready refusal of unverified rules lands with V2-M6. No real rule is verified until the firm names its qualified accountant.</t>
+          <t>Built and tested. The author cannot verify (service 403 and database CHECK). A verified version and its content are immutable (service 409 and database trigger), and changes supersede. Unverified previews carry verified=false and a PREVIEW ONLY notice. Since V2-M6c (DEC-070), the filing-ready package is refused unless the standard version and every size threshold set used were verified by a second person (service), and the database refuses a package under a version never verified. This row is the mechanism only: no real standard content or threshold is verified yet. That is Shoaib's verification in the platform (DEC-052, DEC-056); "ok done" and document reviews verify nothing (DEC-065).</t>
         </is>
       </c>
     </row>
@@ -834,9 +834,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts</t>
+          <t>tests/golden/v2-m6b-workflow.json (docs/architecture/v2-m6b-golden-workings.xlsx re-derives every control and state of five phases with an independent implementation of the rules: 79 checks, 0 differences); tests/api/year-end-workflow.test.ts; tests/unit/year-end-workflow.test.ts; tests/db/year-end-workflow.test.ts; tests/golden/v2-m6c-approval.json (docs/architecture/v2-m6c-golden-workings.xlsx re-derives every control, state and refusal of six phases with an independent implementation of the rules: 112 checks, 0 differences); tests/api/accounts-approval.test.ts; tests/unit/accounts-approval.test.ts; tests/db/accounts-approval.test.ts</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Built in V2-M6b (DEC-069): the 14-step workflow of a framework year with each step's control read from an existing control, its dependencies, its state (LATER, DONE, LAPSED, BLOCKED, TODO, ATTENTION), its sign-offs and the current step; steps 1 to 11 work end to end. Partially: steps 12 to 14 (partner review, client approval, the filing-ready package) arrive with V2-M6c.</t>
+          <t>Built in V2-M6b (DEC-069) and completed in V2-M6c (DEC-070): the 14-step workflow of a framework year. Each step's control is read from an existing control, with its dependencies, its state (DONE, LAPSED, BLOCKED, TODO, ATTENTION), its sign-offs or records, and the current step. Steps 1 to 11 are signed off by a preparer; steps 12 to 14 are done through the partner review, the client approval and the filing-ready package. Proven end to end on synthetic data.</t>
         </is>
       </c>
     </row>
@@ -1689,9 +1689,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1714,8 +1714,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6c-approval.json (docs/architecture/v2-m6c-golden-workings.xlsx re-derives every control, state and refusal of six phases with an independent implementation of the rules: 112 checks, 0 differences); tests/api/accounts-approval.test.ts; tests/unit/accounts-approval.test.ts; tests/db/accounts-approval.test.ts; tests/unit/architecture.test.ts ('approvals and packages have one writer ...')</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Built in V2-M6c (DEC-070). The partner review is recorded by a second person holding accounts:review, who is not the one who signed off the accounts (service 403 and database trigger), against the fingerprint (SHA-256) of the accounts document; it lapses when the accounts change. The client's approval is recorded with the approving director, the date and an evidence document, and must equal the approval the accounts state (Companies Act 2006 s.414). It needs a live partner review and the year's periods closed, and in the same transaction it locks the periods (through the period service) and the year's framework. After it, facts, flag responses, workflow sign-offs and reviews for the year are refused and its periods cannot be unlocked (service and database). Proven on synthetic data. Not built: withdrawing an approval and amended accounts (a later decision).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2821,9 +2829,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2846,10 +2854,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6c-approval.json (docs/architecture/v2-m6c-golden-workings.xlsx re-derives every control, state and refusal of six phases with an independent implementation of the rules: 112 checks, 0 differences); tests/api/accounts-approval.test.ts; tests/unit/accounts-approval.test.ts; tests/db/accounts-approval.test.ts</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+          <t>Built in V2-M6c (DEC-070): done through the partner review, not signed off in the workflow (step_own_record). Its control is the accounts document being complete and, once reviewed, unchanged since the review (READY, or ATTENTION when the accounts changed: LAPSED). Recorded by a second person with accounts:review, with time and an optional note. It is blocked until steps 1 to 11 are all done (DEC-070 amends DEC-069, which had it after step 11 alone). Proven on synthetic data.</t>
         </is>
       </c>
     </row>
@@ -2874,9 +2886,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2899,10 +2911,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6c-approval.json (docs/architecture/v2-m6c-golden-workings.xlsx re-derives every control, state and refusal of six phases with an independent implementation of the rules: 112 checks, 0 differences); tests/api/accounts-approval.test.ts; tests/unit/accounts-approval.test.ts; tests/db/accounts-approval.test.ts</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+          <t>Built in V2-M6c (DEC-070): done through the client approval. Its control is a live partner review, the year's periods closed and the approval facts set; once approved, the accounts unchanged since the approval. It records the director, the date, the evidence, who recorded it and when. Blocked until the partner review is done; it locks the year. Proven on synthetic data.</t>
         </is>
       </c>
     </row>
@@ -2927,9 +2943,9 @@
           <t>V2-M6</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2952,10 +2968,14 @@
           <t>iXBRL and Companies House filing (V3)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>tests/golden/v2-m6c-approval.json (docs/architecture/v2-m6c-golden-workings.xlsx re-derives every control, state and refusal of six phases with an independent implementation of the rules: 112 checks, 0 differences); tests/api/accounts-approval.test.ts; tests/unit/accounts-approval.test.ts; tests/db/accounts-approval.test.ts</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Listed in the V2-M6b workflow as LATER (DEC-069); built with partner review, client approval and the filing-ready package in V2-M6c.</t>
+          <t>Built in V2-M6c (DEC-070): done through the filing-ready package, generated once per year by a preparer and stored write-once with its SHA-256. It holds the approved accounts document, the fingerprint, the framework and who verified it, the size test, the partner review and the client approval. It is refused unless the year is approved, the accounts are unchanged since then and every rule used was verified by a second person (V2-ARC-04). It is not a filing. Proven on synthetic data.</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3939,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json; tests/golden/v2-m6a-review.json; tests/golden/v2-m6b-workflow.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx)</t>
+          <t>tests/golden/v2-m1-micro-synthetic.json; tests/api/statutory.test.ts; tests/golden/v2-m2-fixed-assets.json; tests/golden/v2-m3a-adjustments.json; tests/golden/v2-m3b-close.json; tests/golden/v2-m4-directors.json; tests/golden/v2-m5a-document.json; tests/golden/v2-m5b-size.json; tests/golden/v2-m5c-cash-flow.json; tests/golden/v2-m6a-review.json; tests/golden/v2-m6b-workflow.json (each recomputed independently in its docs/architecture/v2-m*-golden-workings.xlsx); tests/golden/v2-m6c-approval.json</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M6b, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M6b goldens.</t>
+          <t>One micro-entity scenario with two layouts, written by hand first and matched to the cent. One hand figure (the broken-map net assets) was wrong on first run and recalculated by hand (recorded in the golden file). Remaining: scenarios for FRS 102 Section 1A and years with fixed assets and accruals (V2-M2..M5); review of the expected outputs by the named accountant before any real rule is verified. Since then each milestone added a hand-written golden scenario with an independent workbook (V2-M2 to V2-M6c, including the size test over four years and a medium-sized company's cash flow statement over two years); DEC-057 and DEC-061 record Shoaib's review of the V2-M1 to V2-M3b goldens. Still remaining: an FRS 102 Section 1A scenario and the named accountant's review of the V2-M4 to V2-M6c goldens.</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4153,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -4321,7 +4341,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow ACCEPTED 2026-10-21 (v2-m6b-acceptance.md; CI 39595091384 on 9868fbc); V2-M6c approval, locking and the filing-ready package next</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow ACCEPTED 2026-10-21 (v2-m6b-acceptance.md; CI 39595091384 on 9868fbc); V2-M6c partner review, client approval, locking and the filing-ready package BUILT 2026-10-21 (v2-m6c-acceptance.md, DEC-070), evidence pending</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4336,7 +4356,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md sections 5h.3 and 5i.4; v2-m6a-acceptance.md (V2-M6a); v2-m6b-acceptance.md (V2-M6b)</t>
+          <t>v2-plan.md sections 5h.3, 5i.4 and 5j.4; v2-m6a-acceptance.md (V2-M6a); v2-m6b-acceptance.md (V2-M6b); v2-m6c-acceptance.md (V2-M6c)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4348,7 +4368,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -4431,7 +4451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -4441,7 +4461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4451,7 +4471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4490,11 +4510,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>9868fbc</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4502,11 +4518,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39595091384</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4531,7 +4543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4705,6 +4717,13 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v2.3 (2026-10-21, V2-M6c, DEC-070): partner review, client approval, locking and the filing-ready package built. Missing -&gt; Implemented: V2-MOD-15, V2-YE-12 to V2-YE-14. Partially -&gt; Implemented: V2-MOD-01 (all 14 steps) and V2-ARC-04 (the filing-ready refusal of unverified rules; the mechanism only, no real rule verified). V2-TEST-01 gains the V2-M6c golden. The V2-M6b golden is revised for steps 12 to 14, with the revision recorded in the file. Proven on synthetic data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow ACCEPTED 2026-10-21 (v2-m6b-acceptance.md; CI 39595091384 on 9868fbc); V2-M6c partner review, client approval, locking and the filing-ready package BUILT 2026-10-21 (v2-m6c-acceptance.md, DEC-070), evidence pending</t>
+          <t>SPLIT (DEC-068): V2-M6a review flags and the review checklist ACCEPTED 2026-10-21 (v2-m6a-acceptance.md; CI 39575388052 on 8646c7e); V2-M6b the 14-step year-end workflow ACCEPTED 2026-10-21 (v2-m6b-acceptance.md; CI 39595091384 on 9868fbc); V2-M6c partner review, client approval, locking and the filing-ready package ACCEPTED 2026-10-21 (v2-m6c-acceptance.md, DEC-070; CI 39608223030 on 120a949)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4510,7 +4510,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>120a949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4518,7 +4522,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39608223030</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4543,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4724,6 +4732,13 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>v2.3a (2026-10-21): V2-M6c evidence recorded (CI 39608223030 and CodeQL 39608218001 green on 120a949; clean clone 2302 tests, e2e 21/21, OpenAPI drift 0; the first push 0731c7e failed typecheck and was fixed in 120a949).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace in progress (specified in v2-plan 5k); V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>to be specified before code</t>
+          <t>v2-plan.md section 5k (V2-M7a); DEC-050 real-browser proof per slice</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4510,11 +4510,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>120a949</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4522,11 +4518,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39608223030</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3994,8 +3994,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>tests/e2e/year-end.test.ts (V2-M7a: the year-end workspace, five real-browser tests); docs/architecture/v2-m7a-acceptance.md (each screen with its API routes)</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Split into three slices (DEC-071). V2-M7a, the year-end workspace, is built: the workflow, the review checklist and settings, the accounts document with its facts and size test, and the approval and package. It is behind accounts.production and proven in a real browser (DEC-050): the main path from step 11 to the package, a refusal shown in the API's words, a reviewer with no action button, and the feature off. Still missing: V2-M7b, the registers (fixed assets, year-end adjustments, the closing journal, director loans and related parties), and V2-M7c, the reporting framework (standards, verification, thresholds, the framework of each year, the statutory preview and cash flow). Those modules work through the API only, so the row stays Missing until all three slices are accepted.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K62"/>
@@ -4384,7 +4392,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-071): V2-M7a the year-end workspace in progress (specified in v2-plan 5k); V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace BUILT 2026-10-21 (v2-m7a-acceptance.md), evidence pending; V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4399,7 +4407,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5k (V2-M7a); DEC-050 real-browser proof per slice</t>
+          <t>v2-plan.md section 5k (V2-M7a); v2-m7a-acceptance.md; DEC-050 real-browser proof per slice</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4543,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4731,6 +4739,13 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>v2.4 (2026-10-21, V2-M7a, DEC-071): the year-end workspace screens built (workflow, review, accounts, approval and package) and proven in a real browser. V2-DOD-01 stays Missing until V2-M7b and V2-M7c; its note records the slice. No status change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-071): V2-M7a the year-end workspace BUILT 2026-10-21 (v2-m7a-acceptance.md), evidence pending; V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4518,7 +4518,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23b366f</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4526,7 +4530,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39660002000</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4551,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4746,6 +4754,13 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v2.4a (2026-10-21): V2-M7a evidence recorded (CI 39660002000 and CodeQL 39660002001 green on 23b366f; clean clone 2302 tests, e2e 26/26, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4518,11 +4518,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>23b366f</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4530,11 +4526,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39660002000</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4559,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4761,6 +4753,13 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v2.4b (2026-10-21, DEC-072): engineering's data check (a review, not verification). Goldens 905 checks with 0 differences; 44 journals balanced; V2-M1 statements recomputed; 610 evidence paths present; thresholds confirmed against secondary sources; one wording finding (NOTE.CREDLONG). No status change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers and V2-M7c the reporting framework to be specified before their code</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers in progress (specified in v2-plan 5k.3, DEC-074); V2-M7c the reporting framework to be specified before its code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5k (V2-M7a); v2-m7a-acceptance.md; DEC-050 real-browser proof per slice</t>
+          <t>v2-plan.md section 5k (V2-M7a); v2-m7a-acceptance.md; DEC-050 real-browser proof per slice; v2-plan.md section 5k.3 (V2-M7b)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -3996,12 +3996,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>tests/e2e/year-end.test.ts (V2-M7a: the year-end workspace, five real-browser tests); docs/architecture/v2-m7a-acceptance.md (each screen with its API routes)</t>
+          <t>tests/e2e/year-end.test.ts (V2-M7a: the year-end workspace, five real-browser tests); docs/architecture/v2-m7a-acceptance.md (each screen with its API routes); tests/e2e/registers.test.ts (V2-M7b: the registers, six real-browser tests); docs/architecture/v2-m7b-acceptance.md</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Split into three slices (DEC-071). V2-M7a, the year-end workspace, is built: the workflow, the review checklist and settings, the accounts document with its facts and size test, and the approval and package. It is behind accounts.production and proven in a real browser (DEC-050): the main path from step 11 to the package, a refusal shown in the API's words, a reviewer with no action button, and the feature off. Still missing: V2-M7b, the registers (fixed assets, year-end adjustments, the closing journal, director loans and related parties), and V2-M7c, the reporting framework (standards, verification, thresholds, the framework of each year, the statutory preview and cash flow). Those modules work through the API only, so the row stays Missing until all three slices are accepted.</t>
+          <t>Split into three slices (DEC-071). V2-M7a, the year-end workspace, is built: the workflow, the review checklist and settings, the accounts document with its facts and size test, and the approval and package. It is behind accounts.production and proven in a real browser (DEC-050): the main path from step 11 to the package, a refusal shown in the API's words, a reviewer with no action button, and the feature off. V2-M7b, the registers, is built: fixed assets and each asset, depreciation, year-end adjustments and release runs, provisions, the closing journal, director loan accounts and related parties. Proven in a real browser: each register's main action, a refusal shown in the API's words, and a reviewer with no action button. Still missing: V2-M7c, the reporting framework (standards, verification, thresholds, the framework of each year, the statutory preview and cash flow). Those modules work through the API only, so the row stays Missing until V2-M7c is accepted.</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers in progress (specified in v2-plan 5k.3, DEC-074); V2-M7c the reporting framework to be specified before its code</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers BUILT 2026-10-22 (v2-m7b-acceptance.md, DEC-074), evidence pending; V2-M7c the reporting framework to be specified before its code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>v2-plan.md section 5k (V2-M7a); v2-m7a-acceptance.md; DEC-050 real-browser proof per slice; v2-plan.md section 5k.3 (V2-M7b)</t>
+          <t>v2-plan.md section 5k (V2-M7a); v2-m7a-acceptance.md; DEC-050 real-browser proof per slice; v2-plan.md section 5k.3 (V2-M7b); v2-m7b-acceptance.md</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4760,6 +4760,13 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v2.5 (2026-10-22, V2-M7b, DEC-074): the register screens built (fixed assets, depreciation, adjustments, provisions, closing journal, directors, related parties) and proven in a real browser. V2-DOD-01 stays Missing until V2-M7c; its note records the slice. No status change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v2-compliance-matrix.xlsx
+++ b/docs/architecture/v2-compliance-matrix.xlsx
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers BUILT 2026-10-22 (v2-m7b-acceptance.md, DEC-074), evidence pending; V2-M7c the reporting framework to be specified before its code</t>
+          <t>SPLIT (DEC-071): V2-M7a the year-end workspace ACCEPTED 2026-10-21 (v2-m7a-acceptance.md; CI 39660002000 on 23b366f); V2-M7b the registers ACCEPTED 2026-10-22 (v2-m7b-acceptance.md, DEC-074; CI 39776060443 on 2d53914); V2-M7c the reporting framework to be specified before its code</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4518,7 +4518,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2d53914</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4526,7 +4530,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/39776060443</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4551,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4767,6 +4775,13 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v2.5a (2026-10-22): V2-M7b evidence recorded (CI 39776060443 and CodeQL 39776060387 green on 2d53914; clean clone 2302 tests, e2e 32/32, OpenAPI drift 0).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
